--- a/data/trans_dic/P2C_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P2C_R-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Entrevistados que realiza cuidados a personas del hogar que lo requieren</t>
+          <t>Entrevistados que realiza cuidados a personas del hogar que lo requieren (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>75,74; 89,39</t>
+          <t>75,77; 89,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>89,38; 97,18</t>
+          <t>89,32; 97,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>89,14; 96,96</t>
+          <t>88,96; 97,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34,31; 54,13</t>
+          <t>35,1; 54,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>73,97; 87,96</t>
+          <t>74,43; 87,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,94; 96,61</t>
+          <t>88,9; 96,72</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,34; 95,41</t>
+          <t>85,79; 94,89</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>42,0; 62,37</t>
+          <t>44,14; 62,8</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>77,54; 87,25</t>
+          <t>77,78; 86,96</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>90,94; 96,31</t>
+          <t>90,82; 96,37</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>89,08; 95,09</t>
+          <t>89,06; 95,15</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>42,42; 56,01</t>
+          <t>41,63; 55,66</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>80,64; 89,06</t>
+          <t>80,11; 88,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>92,72; 97,65</t>
+          <t>92,37; 97,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>80,63; 90,11</t>
+          <t>81,63; 90,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27,87; 40,1</t>
+          <t>28,0; 40,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>77,43; 86,19</t>
+          <t>77,93; 86,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>87,91; 94,62</t>
+          <t>87,66; 94,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>84,19; 91,5</t>
+          <t>83,96; 91,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>34,24; 47,04</t>
+          <t>35,31; 47,83</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>80,59; 86,59</t>
+          <t>80,4; 86,68</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>90,92; 95,42</t>
+          <t>91,0; 95,51</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>84,14; 89,88</t>
+          <t>84,36; 90,08</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>32,8; 41,69</t>
+          <t>33,49; 42,29</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>56,81; 72,59</t>
+          <t>56,06; 72,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>84,35; 94,99</t>
+          <t>85,3; 95,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>67,47; 79,87</t>
+          <t>67,0; 79,4</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25,91; 38,02</t>
+          <t>25,98; 38,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>61,21; 75,79</t>
+          <t>60,82; 75,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>79,58; 91,51</t>
+          <t>79,85; 91,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>67,86; 80,24</t>
+          <t>68,58; 80,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>21,91; 33,07</t>
+          <t>21,78; 33,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>61,78; 72,47</t>
+          <t>62,02; 72,59</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>84,29; 91,94</t>
+          <t>84,69; 92,07</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>69,09; 77,83</t>
+          <t>69,57; 78,11</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>24,79; 33,59</t>
+          <t>25,24; 33,64</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>39,81; 53,08</t>
+          <t>39,95; 53,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>70,14; 82,59</t>
+          <t>69,74; 83,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>30,6; 45,19</t>
+          <t>30,98; 46,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,11; 29,44</t>
+          <t>16,35; 29,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>37,53; 50,34</t>
+          <t>37,7; 50,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,02; 83,8</t>
+          <t>72,12; 84,04</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,38; 52,76</t>
+          <t>37,37; 52,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>22,6; 37,44</t>
+          <t>22,78; 37,01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>40,44; 49,89</t>
+          <t>40,16; 49,58</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>73,12; 81,72</t>
+          <t>73,56; 82,14</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>36,59; 46,53</t>
+          <t>36,8; 46,92</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>20,93; 30,65</t>
+          <t>21,34; 31,04</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>66,16; 72,69</t>
+          <t>66,23; 72,84</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>87,35; 91,87</t>
+          <t>87,45; 92,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>69,78; 76,16</t>
+          <t>69,63; 76,07</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25,08; 33,2</t>
+          <t>25,46; 33,2</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>65,3; 71,81</t>
+          <t>65,58; 72,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>85,42; 89,91</t>
+          <t>85,3; 90,09</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>72,78; 78,78</t>
+          <t>72,74; 78,6</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>29,57; 36,88</t>
+          <t>29,85; 36,75</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>67,07; 71,51</t>
+          <t>67,03; 71,83</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>87,28; 90,51</t>
+          <t>87,12; 90,35</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72,2; 76,7</t>
+          <t>72,33; 76,42</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>28,78; 33,89</t>
+          <t>28,77; 34,44</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Entrevistados que realiza cuidados a personas del hogar que lo requieren (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>293</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>292</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>65375</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>98130</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>96432</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>25385</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>72882</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>104941</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>89595</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>32886</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>138258</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>203070</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>186027</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>58271</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>59521; 70135</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>93005; 101267</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>91365; 99861</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>20186; 31314</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>65848; 77833</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>99607; 108370</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>84304; 93246</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>27120; 38588</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>129915; 145238</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>196316; 208313</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>178990; 191215</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>49525; 66215</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>471</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>466</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>490</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>159157</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>152329</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>134680</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>53729</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>155414</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>177591</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>185722</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>74291</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>314571</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>329920</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>320402</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>128020</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>150006; 166515</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>147180; 155839</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>127560; 140927</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>44605; 63850</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>147075; 163490</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>169374; 182838</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>176804; 192496</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>64454; 87323</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>302301; 325889</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>320854; 336732</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>309483; 330483</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>114501; 144563</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>56166</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>89106</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>105984</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>55491</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>70827</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>88019</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98213</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>58102</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>126993</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>177126</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>204197</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>113593</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>48479; 63118</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>83581; 93531</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>96684; 114586</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>45184; 67218</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>62804; 77846</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>81298; 92778</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>90638; 106537</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>46288; 70887</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>117685; 137730</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>169206; 183949</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>192351; 215975</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>97507; 129992</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>278</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>70031</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>89374</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>46545</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>63187</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>64698</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>103094</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>58320</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>85766</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>134730</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>192467</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>104865</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>148953</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>60356; 80453</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>80568; 96422</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>37824; 56528</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>45051; 81386</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>55832; 74414</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>94977; 110687</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>48577; 68068</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>69601; 113055</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>120138; 148321</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>181860; 203068</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>92775; 118289</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>123965; 180335</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>520</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>589</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>295</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>545</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>1292</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>1221</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>636</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>350731</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>428939</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>383642</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>197792</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>363821</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>473645</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>431850</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>251045</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>714551</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>902584</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>815492</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>448837</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>333400; 366650</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>417091; 439171</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>365828; 399645</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>169597; 221165</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>346609; 381488</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>459598; 485395</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>415346; 448830</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>227448; 279996</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>691673; 741191</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>884960; 917749</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>792992; 837837</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>410914; 491807</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/P2C_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P2C_R-Edad-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>75,77; 89,28</t>
+          <t>75,67; 89,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>89,32; 97,26</t>
+          <t>89,61; 97,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>88,96; 97,23</t>
+          <t>88,73; 96,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35,1; 54,45</t>
+          <t>34,12; 54,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>74,43; 87,98</t>
+          <t>74,73; 88,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,9; 96,72</t>
+          <t>89,12; 96,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,79; 94,89</t>
+          <t>85,19; 94,88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>44,14; 62,8</t>
+          <t>43,44; 63,1</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>77,78; 86,96</t>
+          <t>77,67; 87,01</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>90,82; 96,37</t>
+          <t>90,82; 96,26</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>89,06; 95,15</t>
+          <t>89,18; 95,11</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>41,63; 55,66</t>
+          <t>41,84; 56,5</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>80,11; 88,93</t>
+          <t>80,65; 89,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>92,37; 97,8</t>
+          <t>92,44; 97,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>81,63; 90,18</t>
+          <t>81,11; 90,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28,0; 40,08</t>
+          <t>28,26; 40,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>77,93; 86,63</t>
+          <t>77,81; 86,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>87,66; 94,62</t>
+          <t>88,07; 94,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>83,96; 91,41</t>
+          <t>84,45; 91,6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>35,31; 47,83</t>
+          <t>34,76; 47,06</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>80,4; 86,68</t>
+          <t>80,7; 86,56</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>91,0; 95,51</t>
+          <t>91,18; 95,62</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>84,36; 90,08</t>
+          <t>84,32; 89,84</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>33,49; 42,29</t>
+          <t>33,47; 41,87</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>56,06; 72,99</t>
+          <t>56,65; 72,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>85,3; 95,46</t>
+          <t>85,39; 95,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>67,0; 79,4</t>
+          <t>67,31; 79,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25,98; 38,66</t>
+          <t>25,85; 37,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>60,82; 75,39</t>
+          <t>61,2; 75,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>79,85; 91,13</t>
+          <t>79,99; 91,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>68,58; 80,61</t>
+          <t>67,39; 79,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>21,78; 33,36</t>
+          <t>22,16; 33,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>62,02; 72,59</t>
+          <t>61,16; 72,04</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>84,69; 92,07</t>
+          <t>84,31; 91,9</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>69,57; 78,11</t>
+          <t>68,84; 77,95</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>25,24; 33,64</t>
+          <t>25,22; 33,91</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>39,95; 53,25</t>
+          <t>39,61; 53,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>69,74; 83,47</t>
+          <t>69,95; 82,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>30,98; 46,29</t>
+          <t>30,67; 46,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,35; 29,55</t>
+          <t>16,73; 29,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>37,7; 50,25</t>
+          <t>36,69; 50,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,12; 84,04</t>
+          <t>71,92; 84,01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,37; 52,36</t>
+          <t>37,86; 51,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>22,78; 37,01</t>
+          <t>22,46; 36,67</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>40,16; 49,58</t>
+          <t>39,85; 49,45</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>73,56; 82,14</t>
+          <t>73,62; 81,93</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>36,8; 46,92</t>
+          <t>36,79; 47,11</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>21,34; 31,04</t>
+          <t>20,81; 31,04</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>66,23; 72,84</t>
+          <t>66,48; 72,97</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>87,45; 92,08</t>
+          <t>87,71; 91,95</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>69,63; 76,07</t>
+          <t>69,96; 76,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25,46; 33,2</t>
+          <t>25,47; 33,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>65,58; 72,18</t>
+          <t>65,6; 72,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>85,3; 90,09</t>
+          <t>85,66; 90,27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>72,74; 78,6</t>
+          <t>72,45; 78,47</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>29,85; 36,75</t>
+          <t>29,46; 37,15</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>67,03; 71,83</t>
+          <t>66,82; 71,58</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>87,12; 90,35</t>
+          <t>87,09; 90,42</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72,33; 76,42</t>
+          <t>72,17; 76,44</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>28,77; 34,44</t>
+          <t>28,7; 33,82</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>59521; 70135</t>
+          <t>59444; 70159</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>93005; 101267</t>
+          <t>93299; 101000</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>91365; 99861</t>
+          <t>91130; 99243</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20186; 31314</t>
+          <t>19624; 31159</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>65848; 77833</t>
+          <t>66105; 78098</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>99607; 108370</t>
+          <t>99852; 108480</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>84304; 93246</t>
+          <t>83713; 93233</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>27120; 38588</t>
+          <t>26692; 38768</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>129915; 145238</t>
+          <t>129720; 145325</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>196316; 208313</t>
+          <t>196325; 208083</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>178990; 191215</t>
+          <t>179220; 191153</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>49525; 66215</t>
+          <t>49773; 67211</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>150006; 166515</t>
+          <t>151013; 166811</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>147180; 155839</t>
+          <t>147304; 155620</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>127560; 140927</t>
+          <t>126753; 140958</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>44605; 63850</t>
+          <t>45016; 64014</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>147075; 163490</t>
+          <t>146853; 163230</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>169374; 182838</t>
+          <t>170163; 183080</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>176804; 192496</t>
+          <t>177842; 192902</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>64454; 87323</t>
+          <t>63458; 85907</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>302301; 325889</t>
+          <t>303408; 325438</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>320854; 336732</t>
+          <t>321459; 337116</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>309483; 330483</t>
+          <t>309327; 329597</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>114501; 144563</t>
+          <t>114413; 143135</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>48479; 63118</t>
+          <t>48986; 62959</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>83581; 93531</t>
+          <t>83663; 93368</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>96684; 114586</t>
+          <t>97135; 114362</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>45184; 67218</t>
+          <t>44953; 66025</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>62804; 77846</t>
+          <t>63199; 77738</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>81298; 92778</t>
+          <t>81434; 93028</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>90638; 106537</t>
+          <t>89064; 105686</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>46288; 70887</t>
+          <t>47089; 70550</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>117685; 137730</t>
+          <t>116038; 136685</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>169206; 183949</t>
+          <t>168445; 183605</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>192351; 215975</t>
+          <t>190344; 215515</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>97507; 129992</t>
+          <t>97443; 131009</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>60356; 80453</t>
+          <t>59848; 80277</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>80568; 96422</t>
+          <t>80809; 95615</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>37824; 56528</t>
+          <t>37445; 56179</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>45051; 81386</t>
+          <t>46076; 82225</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>55832; 74414</t>
+          <t>54331; 74418</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>94977; 110687</t>
+          <t>94725; 110648</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>48577; 68068</t>
+          <t>49223; 67521</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>69601; 113055</t>
+          <t>68618; 112025</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>120138; 148321</t>
+          <t>119224; 147950</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>181860; 203068</t>
+          <t>182002; 202556</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>92775; 118289</t>
+          <t>92754; 118761</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>123965; 180335</t>
+          <t>120899; 180317</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>333400; 366650</t>
+          <t>334656; 367316</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>417091; 439171</t>
+          <t>418324; 438557</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>365828; 399645</t>
+          <t>367557; 401043</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>169597; 221165</t>
+          <t>169639; 220990</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>346609; 381488</t>
+          <t>346730; 380608</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>459598; 485395</t>
+          <t>461494; 486339</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>415346; 448830</t>
+          <t>413730; 448105</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>227448; 279996</t>
+          <t>224471; 283042</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>691673; 741191</t>
+          <t>689538; 738597</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>884960; 917749</t>
+          <t>884572; 918467</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>792992; 837837</t>
+          <t>791295; 838073</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>410914; 491807</t>
+          <t>409924; 482981</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2C_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P2C_R-Edad-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>82,39%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>93,66%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>91,18%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>53,11%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>83,22%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>94,25%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>93,89%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>44,14%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>82,39%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>93,66%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>91,18%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>42,37%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>47,66%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>75,67; 89,31</t>
+          <t>73,97; 87,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>89,61; 97,0</t>
+          <t>88,94; 96,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>88,73; 96,63</t>
+          <t>86,34; 95,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34,12; 54,18</t>
+          <t>41,63; 61,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>74,73; 88,28</t>
+          <t>75,74; 89,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,12; 96,82</t>
+          <t>89,38; 97,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,19; 94,88</t>
+          <t>89,14; 96,96</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>43,44; 63,1</t>
+          <t>32,4; 52,48</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>77,67; 87,01</t>
+          <t>77,54; 87,25</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>90,82; 96,26</t>
+          <t>90,94; 96,31</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>89,18; 95,11</t>
+          <t>89,08; 95,09</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>41,84; 56,5</t>
+          <t>41,31; 54,72</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>82,35%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>91,91%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>88,19%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>41,34%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>85,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>95,6%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>86,19%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>33,73%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>82,35%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>91,91%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>88,19%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>38,47%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>80,65; 89,09</t>
+          <t>77,43; 86,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>92,44; 97,66</t>
+          <t>87,91; 94,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>81,11; 90,2</t>
+          <t>84,19; 91,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28,26; 40,18</t>
+          <t>34,59; 47,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>77,81; 86,49</t>
+          <t>80,64; 89,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>88,07; 94,75</t>
+          <t>92,72; 97,65</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>84,45; 91,6</t>
+          <t>80,63; 90,11</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>34,76; 47,06</t>
+          <t>29,48; 41,6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>80,7; 86,56</t>
+          <t>80,59; 86,59</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>91,18; 95,62</t>
+          <t>90,92; 95,42</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>84,32; 89,84</t>
+          <t>84,14; 89,88</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>33,47; 41,87</t>
+          <t>33,67; 42,91</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>68,59%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>86,45%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>74,31%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>29,51%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>64,95%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>90,94%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>73,44%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>31,91%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>68,59%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>86,45%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>74,31%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>31,56%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>56,65; 72,8</t>
+          <t>61,21; 75,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>85,39; 95,29</t>
+          <t>79,58; 91,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>67,31; 79,25</t>
+          <t>67,86; 80,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25,85; 37,97</t>
+          <t>23,76; 35,39</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>61,2; 75,28</t>
+          <t>56,81; 72,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>79,99; 91,37</t>
+          <t>84,35; 94,99</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>67,39; 79,96</t>
+          <t>67,47; 79,87</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>22,16; 33,2</t>
+          <t>27,91; 40,21</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>61,16; 72,04</t>
+          <t>61,78; 72,47</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>84,31; 91,9</t>
+          <t>84,29; 91,94</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>68,84; 77,95</t>
+          <t>69,09; 77,83</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>25,22; 33,91</t>
+          <t>27,05; 35,81</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>43,69%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>78,28%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>44,86%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>29,51%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>46,36%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>77,37%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>38,12%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>22,94%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>43,69%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>78,28%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>44,86%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>27,0%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>39,61; 53,14</t>
+          <t>37,53; 50,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>69,95; 82,77</t>
+          <t>72,02; 83,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>30,67; 46,01</t>
+          <t>37,38; 52,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,73; 29,85</t>
+          <t>23,92; 37,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>36,69; 50,25</t>
+          <t>39,81; 53,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,92; 84,01</t>
+          <t>70,14; 82,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,86; 51,94</t>
+          <t>30,6; 45,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>22,46; 36,67</t>
+          <t>19,56; 28,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>39,85; 49,45</t>
+          <t>40,44; 49,89</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>73,62; 81,93</t>
+          <t>73,12; 81,72</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>36,79; 47,11</t>
+          <t>36,59; 46,53</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>20,81; 31,04</t>
+          <t>22,96; 31,7</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>68,83%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>87,91%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>75,63%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>33,87%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>69,68%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>89,93%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>73,02%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>29,69%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>68,83%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>87,91%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>75,63%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>32,49%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>66,48; 72,97</t>
+          <t>65,3; 71,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>87,71; 91,95</t>
+          <t>85,42; 89,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>69,96; 76,33</t>
+          <t>72,78; 78,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25,47; 33,17</t>
+          <t>30,61; 37,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>65,6; 72,01</t>
+          <t>66,16; 72,69</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>85,66; 90,27</t>
+          <t>87,35; 91,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>72,45; 78,47</t>
+          <t>69,78; 76,16</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>29,46; 37,15</t>
+          <t>28,03; 34,14</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>66,82; 71,58</t>
+          <t>67,07; 71,51</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>87,09; 90,42</t>
+          <t>87,28; 90,51</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72,17; 76,44</t>
+          <t>72,2; 76,7</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>28,7; 33,82</t>
+          <t>30,14; 34,7</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>145</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>155</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>52</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>72882</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>104941</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>89595</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>26842</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>65375</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>98130</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>96432</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>25385</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>72882</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>104941</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>89595</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>32886</t>
+          <t>22070</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>58271</t>
+          <t>48912</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>59444; 70159</t>
+          <t>65437; 77813</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>93299; 101000</t>
+          <t>99652; 108245</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>91130; 99243</t>
+          <t>84848; 93755</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19624; 31159</t>
+          <t>21038; 31315</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>66105; 78098</t>
+          <t>59497; 70227</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>99852; 108480</t>
+          <t>93059; 101190</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>83713; 93233</t>
+          <t>91548; 99578</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>26692; 38768</t>
+          <t>16880; 27338</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>129720; 145325</t>
+          <t>129505; 145723</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>196325; 208083</t>
+          <t>196584; 208179</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>179220; 191153</t>
+          <t>179035; 191111</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>49773; 67211</t>
+          <t>42398; 56157</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>238</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>220</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>215</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>89</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>155414</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>177591</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>185722</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>65113</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>159157</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>152329</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>134680</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>53729</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>155414</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>177591</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>185722</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>74291</t>
+          <t>51478</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>128020</t>
+          <t>116590</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>151013; 166811</t>
+          <t>146139; 162676</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>147304; 155620</t>
+          <t>169871; 182825</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>126753; 140958</t>
+          <t>177287; 192681</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>45016; 64014</t>
+          <t>54480; 75488</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>146853; 163230</t>
+          <t>150990; 166768</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>170163; 183080</t>
+          <t>147748; 155597</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>177842; 192902</t>
+          <t>125989; 140817</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>63458; 85907</t>
+          <t>42904; 60541</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>303408; 325438</t>
+          <t>302999; 325540</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>321459; 337116</t>
+          <t>320556; 336420</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>309327; 329597</t>
+          <t>308674; 329721</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>114413; 143135</t>
+          <t>102030; 130045</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>126</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>153</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>73</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>70827</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>88019</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>98213</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>59062</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>56166</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>89106</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>105984</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>55491</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>70827</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>88019</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98213</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>58102</t>
+          <t>59477</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>113593</t>
+          <t>118539</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>48986; 62959</t>
+          <t>63207; 78261</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>83663; 93368</t>
+          <t>81020; 93165</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>97135; 114362</t>
+          <t>89692; 106047</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>44953; 66025</t>
+          <t>47543; 70815</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>63199; 77738</t>
+          <t>49129; 62775</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>81434; 93028</t>
+          <t>82645; 93076</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>89064; 105686</t>
+          <t>97370; 115263</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>47089; 70550</t>
+          <t>48993; 70578</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>116038; 136685</t>
+          <t>117230; 137501</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>168445; 183605</t>
+          <t>168402; 183696</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>190344; 215515</t>
+          <t>191011; 215186</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>97443; 131009</t>
+          <t>101597; 134503</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>126</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>81</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>64698</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>103094</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>58320</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>86350</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>70031</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>89374</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>46545</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>63187</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>64698</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>103094</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>58320</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>85766</t>
+          <t>61957</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>148953</t>
+          <t>148307</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>59848; 80277</t>
+          <t>55579; 74545</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>80809; 95615</t>
+          <t>94846; 110364</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>37445; 56179</t>
+          <t>48591; 68596</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>46076; 82225</t>
+          <t>70011; 108996</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>54331; 74418</t>
+          <t>60137; 80189</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>94725; 110648</t>
+          <t>81024; 95413</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>49223; 67521</t>
+          <t>37361; 55176</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>68618; 112025</t>
+          <t>50181; 74226</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>119224; 147950</t>
+          <t>120986; 149266</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>182002; 202556</t>
+          <t>180757; 202036</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>92754; 118761</t>
+          <t>92235; 117315</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>120899; 180317</t>
+          <t>126100; 174080</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>545</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>520</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>617</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>589</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>295</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>545</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>675</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>632</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>341</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>363821</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>473645</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>431850</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>237366</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>350731</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>428939</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>383642</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>197792</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>363821</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>473645</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>431850</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>251045</t>
+          <t>194981</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>448837</t>
+          <t>432348</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>334656; 367316</t>
+          <t>345138; 379567</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>418324; 438557</t>
+          <t>460235; 484394</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>367557; 401043</t>
+          <t>415584; 449887</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>169639; 220990</t>
+          <t>214504; 264437</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>346730; 380608</t>
+          <t>333008; 365889</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>461494; 486339</t>
+          <t>416621; 438190</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>413730; 448105</t>
+          <t>366597; 400140</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>224471; 283042</t>
+          <t>176518; 214951</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>689538; 738597</t>
+          <t>692115; 737936</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>884572; 918467</t>
+          <t>886523; 919393</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>791295; 838073</t>
+          <t>791620; 840951</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>409924; 482981</t>
+          <t>400997; 461688</t>
         </is>
       </c>
     </row>
